--- a/Reports.xlsx
+++ b/Reports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GN0072\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD252C94-D4E4-4169-A934-7B8EFCF83665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05707F86-C70B-4012-A1EE-505FDFAAE319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="10008" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reports" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="470">
   <si>
     <t>Source</t>
   </si>
@@ -184,6 +184,9 @@
 </t>
   </si>
   <si>
+    <t>NH_Identity_Internal_Audit_Report</t>
+  </si>
+  <si>
     <t>NOV_SecAdmin Group Audit</t>
   </si>
   <si>
@@ -312,6 +315,9 @@
   <si>
     <t xml:space="preserve">Manually run and saved in  \\corpshare\corp\IAM_Audit\epic\empedit
 </t>
+  </si>
+  <si>
+    <t>Sahaja</t>
   </si>
   <si>
     <t>Epic EMP Full</t>
@@ -443,6 +449,9 @@
     <t>Report of all organizational cost centers</t>
   </si>
   <si>
+    <t>NH_CostCenters_Report</t>
+  </si>
+  <si>
     <t>Daily AD User Report</t>
   </si>
   <si>
@@ -456,6 +465,9 @@
   </si>
   <si>
     <t>SQL-Infor</t>
+  </si>
+  <si>
+    <t>NH_Entities_Report</t>
   </si>
   <si>
     <t>Export AD Group Membership</t>
@@ -474,6 +486,9 @@
 SQL-OneIdentity/, SQL-Infor</t>
   </si>
   <si>
+    <t>NH_Payable_Term_Report</t>
+  </si>
+  <si>
     <t>Get MemberOf</t>
   </si>
   <si>
@@ -748,6 +763,9 @@
     <t>CCC_EmployeeTerminationCount-Total</t>
   </si>
   <si>
+    <t>NH_Report_Total_IAM_TerminatesIn_LastMonth</t>
+  </si>
+  <si>
     <t>CCC_PWMInitiationsCount-Quarter</t>
   </si>
   <si>
@@ -973,6 +991,9 @@
     <t>Active contractor identifiers from source</t>
   </si>
   <si>
+    <t>NH_CCC_ContractorIdentifiers</t>
+  </si>
+  <si>
     <t>CCC_ContractorManagers</t>
   </si>
   <si>
@@ -1060,6 +1081,9 @@
     <t>MGR Onboarding</t>
   </si>
   <si>
+    <t>NH_MGR_Onboarding_Report</t>
+  </si>
+  <si>
     <t>CCC_NewEmployeesLast24Hours</t>
   </si>
   <si>
@@ -1120,6 +1144,12 @@
     <t>Non-Novant Worker End dates</t>
   </si>
   <si>
+    <t>inprogress</t>
+  </si>
+  <si>
+    <t>NH_NNE_EndDates_Report</t>
+  </si>
+  <si>
     <t>CCC_NonEmployeesWithEmail</t>
   </si>
   <si>
@@ -1393,9 +1423,6 @@
     <t>NH_Report_Onboarded_Users</t>
   </si>
   <si>
-    <t>NH_Report_Total_IAM_TerminatesIn_LastMonth</t>
-  </si>
-  <si>
     <t>NH_Report_Total_Service_Accounts</t>
   </si>
   <si>
@@ -1421,6 +1448,36 @@
   </si>
   <si>
     <t>NH_Time_To_Provision(TTP) Report</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_LeavingDate_With_Usertype" "NH_Report_LeavingDate_With_Usertype.xml" -clean</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_NH_Link_New_Hires" "NH_Report_NH_Link_New_Hires.xml" -clean</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_Missing_corpID" "NH_Report_Missing_corpID.xml" -clean</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_Missing_Managers" "NH_Report_Missing_Managers.xml" -clean</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_Missing_UPN" "NH_Report_Missing_UPN.xml" -clean</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_Missing_PersonID" "NH_Report_Missing_PersonID.xml" -clean</t>
+  </si>
+  <si>
+    <t>NH_Report_Total_NonHuman_Active_Accounts</t>
+  </si>
+  <si>
+    <t>checkout TaskDefinition "NH_Report_Total_NonHuman_Active_Accounts" "NH_Report_Total_NonHuman_Active_Accounts.xml" -clean</t>
+  </si>
+  <si>
+    <t>javabased</t>
   </si>
 </sst>
 </file>
@@ -2073,12 +2130,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7790F-BFFF-4C75-BDC2-60CFF6F25A9C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N196"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="14.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="34.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="42.42578125" style="1" customWidth="1"/>
@@ -2134,7 +2192,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="117.75" customHeight="1">
+    <row r="2" spans="1:14" ht="117.75" hidden="1" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2227,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:14" s="7" customFormat="1" ht="101.25">
+    <row r="3" spans="1:14" s="7" customFormat="1" ht="101.25" hidden="1">
       <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
@@ -2197,7 +2255,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
     </row>
-    <row r="4" spans="1:14" ht="87">
+    <row r="4" spans="1:14" ht="87" hidden="1">
       <c r="A4" s="11" t="s">
         <v>12</v>
       </c>
@@ -2257,7 +2315,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" ht="144.75">
+    <row r="6" spans="1:14" ht="144.75" hidden="1">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
@@ -2279,6 +2337,12 @@
       <c r="I6" s="11" t="s">
         <v>34</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -2291,11 +2355,11 @@
         <v>13</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -2305,7 +2369,7 @@
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" s="7" customFormat="1" ht="30.75">
+    <row r="8" spans="1:14" s="7" customFormat="1" ht="30.75" hidden="1">
       <c r="A8" s="11" t="s">
         <v>12</v>
       </c>
@@ -2313,7 +2377,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="18"/>
@@ -2333,17 +2397,17 @@
         <v>13</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="11"/>
@@ -2351,7 +2415,7 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:14" s="7" customFormat="1" ht="121.5">
+    <row r="10" spans="1:14" s="7" customFormat="1" ht="121.5" hidden="1">
       <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
@@ -2359,16 +2423,16 @@
         <v>22</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="20"/>
@@ -2376,10 +2440,10 @@
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="48.75" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="48.75" hidden="1" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>12</v>
       </c>
@@ -2387,19 +2451,19 @@
         <v>13</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>33</v>
@@ -2408,7 +2472,7 @@
         <v>34</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>20</v>
@@ -2425,19 +2489,19 @@
         <v>13</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="11"/>
@@ -2453,19 +2517,19 @@
         <v>13</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="11"/>
@@ -2481,17 +2545,17 @@
         <v>13</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="11"/>
@@ -2507,19 +2571,19 @@
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="11"/>
@@ -2535,19 +2599,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="11"/>
@@ -2563,19 +2627,19 @@
         <v>13</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="11"/>
@@ -2591,22 +2655,24 @@
         <v>13</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
@@ -2619,22 +2685,24 @@
         <v>13</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
@@ -2647,19 +2715,19 @@
         <v>13</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="11"/>
@@ -2675,17 +2743,17 @@
         <v>13</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="11"/>
@@ -2693,7 +2761,7 @@
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
     </row>
-    <row r="22" spans="1:14" ht="87">
+    <row r="22" spans="1:14" ht="87" hidden="1">
       <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
@@ -2701,34 +2769,34 @@
         <v>13</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
       <c r="N22" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="60.75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="60.75" hidden="1">
       <c r="A23" s="11" t="s">
         <v>12</v>
       </c>
@@ -2736,17 +2804,17 @@
         <v>13</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>33</v>
@@ -2758,7 +2826,7 @@
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" spans="1:14" s="7" customFormat="1" ht="30.75">
+    <row r="24" spans="1:14" s="7" customFormat="1" ht="30.75" hidden="1">
       <c r="A24" s="11" t="s">
         <v>12</v>
       </c>
@@ -2766,17 +2834,17 @@
         <v>22</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>102</v>
       </c>
       <c r="H24" s="20" t="s">
         <v>33</v>
@@ -2796,19 +2864,19 @@
         <v>13</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="11"/>
@@ -2826,19 +2894,19 @@
         <v>13</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="11"/>
@@ -2856,19 +2924,19 @@
         <v>13</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="11"/>
@@ -2884,19 +2952,19 @@
         <v>13</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H28" s="34"/>
       <c r="I28" s="11"/>
@@ -2904,7 +2972,7 @@
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
     </row>
-    <row r="29" spans="1:14" ht="29.25">
+    <row r="29" spans="1:14" ht="29.25" hidden="1">
       <c r="A29" s="11" t="s">
         <v>12</v>
       </c>
@@ -2912,22 +2980,22 @@
         <v>22</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>34</v>
@@ -2936,7 +3004,7 @@
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
     </row>
-    <row r="30" spans="1:14" ht="29.25">
+    <row r="30" spans="1:14" ht="29.25" hidden="1">
       <c r="A30" s="11" t="s">
         <v>12</v>
       </c>
@@ -2944,31 +3012,37 @@
         <v>13</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>33</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>34</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
     </row>
-    <row r="31" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="31" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -2976,19 +3050,19 @@
         <v>22</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H31" s="20" t="s">
         <v>33</v>
@@ -3000,7 +3074,7 @@
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
     </row>
-    <row r="32" spans="1:14" ht="29.25">
+    <row r="32" spans="1:14" ht="29.25" hidden="1">
       <c r="A32" s="11" t="s">
         <v>12</v>
       </c>
@@ -3008,31 +3082,37 @@
         <v>13</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>34</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
     </row>
-    <row r="33" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="33" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A33" s="11" t="s">
         <v>12</v>
       </c>
@@ -3040,19 +3120,19 @@
         <v>22</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H33" s="20" t="s">
         <v>33</v>
@@ -3064,7 +3144,7 @@
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
     </row>
-    <row r="34" spans="1:14" ht="72.75">
+    <row r="34" spans="1:14" ht="72.75" hidden="1">
       <c r="A34" s="11" t="s">
         <v>12</v>
       </c>
@@ -3072,27 +3152,37 @@
         <v>13</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="10"/>
-      <c r="I34" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
     </row>
-    <row r="35" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="35" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A35" s="11" t="s">
         <v>12</v>
       </c>
@@ -3100,19 +3190,19 @@
         <v>22</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H35" s="20" t="s">
         <v>33</v>
@@ -3124,7 +3214,7 @@
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
     </row>
-    <row r="36" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="36" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A36" s="11" t="s">
         <v>12</v>
       </c>
@@ -3132,19 +3222,19 @@
         <v>22</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>33</v>
@@ -3156,7 +3246,7 @@
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
     </row>
-    <row r="37" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="37" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A37" s="11" t="s">
         <v>12</v>
       </c>
@@ -3164,19 +3254,19 @@
         <v>22</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>33</v>
@@ -3188,7 +3278,7 @@
       <c r="M37" s="12"/>
       <c r="N37" s="12"/>
     </row>
-    <row r="38" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="38" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A38" s="11" t="s">
         <v>12</v>
       </c>
@@ -3196,19 +3286,19 @@
         <v>22</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>33</v>
@@ -3217,7 +3307,7 @@
         <v>34</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>20</v>
@@ -3226,7 +3316,7 @@
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
     </row>
-    <row r="39" spans="1:14" ht="29.25">
+    <row r="39" spans="1:14" ht="29.25" hidden="1">
       <c r="A39" s="11" t="s">
         <v>12</v>
       </c>
@@ -3234,19 +3324,19 @@
         <v>13</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>33</v>
@@ -3255,7 +3345,7 @@
         <v>34</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>20</v>
@@ -3264,7 +3354,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" ht="29.25">
+    <row r="40" spans="1:14" ht="29.25" hidden="1">
       <c r="A40" s="11" t="s">
         <v>12</v>
       </c>
@@ -3272,19 +3362,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>33</v>
@@ -3293,7 +3383,7 @@
         <v>34</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>20</v>
@@ -3302,7 +3392,7 @@
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
     </row>
-    <row r="41" spans="1:14" ht="29.25">
+    <row r="41" spans="1:14" ht="29.25" hidden="1">
       <c r="A41" s="11" t="s">
         <v>12</v>
       </c>
@@ -3310,19 +3400,19 @@
         <v>13</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>33</v>
@@ -3331,7 +3421,7 @@
         <v>34</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>20</v>
@@ -3340,7 +3430,7 @@
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
     </row>
-    <row r="42" spans="1:14" ht="29.25">
+    <row r="42" spans="1:14" ht="29.25" hidden="1">
       <c r="A42" s="11" t="s">
         <v>12</v>
       </c>
@@ -3348,19 +3438,19 @@
         <v>13</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H42" s="11" t="s">
         <v>33</v>
@@ -3369,7 +3459,7 @@
         <v>34</v>
       </c>
       <c r="J42" s="49" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>20</v>
@@ -3378,7 +3468,7 @@
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
     </row>
-    <row r="43" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="43" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A43" s="11" t="s">
         <v>12</v>
       </c>
@@ -3386,19 +3476,19 @@
         <v>22</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>33</v>
@@ -3410,7 +3500,7 @@
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14" ht="29.25">
+    <row r="44" spans="1:14" ht="29.25" hidden="1">
       <c r="A44" s="11" t="s">
         <v>12</v>
       </c>
@@ -3418,19 +3508,19 @@
         <v>22</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>33</v>
@@ -3442,7 +3532,7 @@
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
     </row>
-    <row r="45" spans="1:14" ht="29.25">
+    <row r="45" spans="1:14" ht="29.25" hidden="1">
       <c r="A45" s="11" t="s">
         <v>12</v>
       </c>
@@ -3450,19 +3540,19 @@
         <v>22</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>33</v>
@@ -3474,7 +3564,7 @@
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
     </row>
-    <row r="46" spans="1:14" ht="57.75">
+    <row r="46" spans="1:14" ht="57.75" hidden="1">
       <c r="A46" s="11" t="s">
         <v>12</v>
       </c>
@@ -3482,19 +3572,19 @@
         <v>22</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>33</v>
@@ -3506,7 +3596,7 @@
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
     </row>
-    <row r="47" spans="1:14" ht="29.25">
+    <row r="47" spans="1:14" ht="29.25" hidden="1">
       <c r="A47" s="11" t="s">
         <v>12</v>
       </c>
@@ -3514,19 +3604,19 @@
         <v>22</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H47" s="11" t="s">
         <v>33</v>
@@ -3538,7 +3628,7 @@
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
     </row>
-    <row r="48" spans="1:14" ht="29.25">
+    <row r="48" spans="1:14" ht="29.25" hidden="1">
       <c r="A48" s="11" t="s">
         <v>12</v>
       </c>
@@ -3546,17 +3636,17 @@
         <v>13</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F48" s="11"/>
       <c r="G48" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>33</v>
@@ -3565,7 +3655,7 @@
         <v>34</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>20</v>
@@ -3574,7 +3664,7 @@
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
     </row>
-    <row r="49" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="49" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A49" s="11" t="s">
         <v>12</v>
       </c>
@@ -3582,19 +3672,19 @@
         <v>22</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>33</v>
@@ -3606,7 +3696,7 @@
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
     </row>
-    <row r="50" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="50" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A50" s="11" t="s">
         <v>12</v>
       </c>
@@ -3614,19 +3704,19 @@
         <v>22</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>33</v>
@@ -3638,7 +3728,7 @@
       <c r="M50" s="12"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="51" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A51" s="11" t="s">
         <v>12</v>
       </c>
@@ -3646,19 +3736,19 @@
         <v>22</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="12"/>
@@ -3666,7 +3756,7 @@
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="52" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A52" s="11" t="s">
         <v>12</v>
       </c>
@@ -3674,19 +3764,19 @@
         <v>22</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>33</v>
@@ -3698,7 +3788,7 @@
       <c r="M52" s="12"/>
       <c r="N52" s="12"/>
     </row>
-    <row r="53" spans="1:14" s="7" customFormat="1">
+    <row r="53" spans="1:14" s="7" customFormat="1" hidden="1">
       <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
@@ -3706,19 +3796,19 @@
         <v>22</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="12"/>
@@ -3726,7 +3816,7 @@
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
     </row>
-    <row r="54" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="54" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A54" s="11" t="s">
         <v>12</v>
       </c>
@@ -3734,19 +3824,19 @@
         <v>22</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
@@ -3754,7 +3844,7 @@
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
     </row>
-    <row r="55" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="55" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A55" s="11" t="s">
         <v>12</v>
       </c>
@@ -3762,19 +3852,19 @@
         <v>22</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>33</v>
@@ -3794,19 +3884,19 @@
         <v>13</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
@@ -3822,19 +3912,19 @@
         <v>13</v>
       </c>
       <c r="C57" s="33" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
@@ -3850,19 +3940,19 @@
         <v>13</v>
       </c>
       <c r="C58" s="33" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
@@ -3870,7 +3960,7 @@
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
     </row>
-    <row r="59" spans="1:14" s="7" customFormat="1" ht="60.75">
+    <row r="59" spans="1:14" s="7" customFormat="1" ht="60.75" hidden="1">
       <c r="A59" s="11" t="s">
         <v>12</v>
       </c>
@@ -3878,29 +3968,29 @@
         <v>22</v>
       </c>
       <c r="C59" s="41" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
     </row>
-    <row r="60" spans="1:14" s="7" customFormat="1" ht="76.5">
+    <row r="60" spans="1:14" s="7" customFormat="1" ht="76.5" hidden="1">
       <c r="A60" s="11" t="s">
         <v>12</v>
       </c>
@@ -3908,19 +3998,19 @@
         <v>22</v>
       </c>
       <c r="C60" s="42" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="43" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>33</v>
@@ -3930,7 +4020,7 @@
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
     </row>
-    <row r="61" spans="1:14" s="7" customFormat="1" ht="29.25">
+    <row r="61" spans="1:14" s="7" customFormat="1" ht="29.25" hidden="1">
       <c r="A61" s="11" t="s">
         <v>12</v>
       </c>
@@ -3938,19 +4028,19 @@
         <v>22</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="12"/>
@@ -3958,7 +4048,7 @@
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" hidden="1">
       <c r="A62" s="11" t="s">
         <v>12</v>
       </c>
@@ -3966,19 +4056,19 @@
         <v>13</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H62" s="11" t="s">
         <v>33</v>
@@ -3987,7 +4077,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>20</v>
@@ -3998,17 +4088,17 @@
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
       <c r="A63" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="11" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
@@ -4020,17 +4110,17 @@
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F64" s="11"/>
       <c r="G64" s="11"/>
@@ -4042,17 +4132,17 @@
     </row>
     <row r="65" spans="1:14" ht="15" customHeight="1">
       <c r="A65" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
@@ -4064,50 +4154,52 @@
     </row>
     <row r="66" spans="1:14" ht="15" customHeight="1">
       <c r="A66" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F66" s="11"/>
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
+      <c r="I66" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="L66" s="11"/>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
     </row>
-    <row r="67" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="67" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A67" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B67" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C67" s="44" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D67" s="44"/>
       <c r="E67" s="44" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F67" s="44"/>
       <c r="G67" s="44"/>
       <c r="H67" s="13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I67" s="44" t="s">
         <v>20</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K67" s="50"/>
       <c r="L67" s="38"/>
@@ -4116,17 +4208,17 @@
     </row>
     <row r="68" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B68" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="44" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D68" s="44"/>
       <c r="E68" s="44" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F68" s="44"/>
       <c r="G68" s="44"/>
@@ -4138,17 +4230,17 @@
     </row>
     <row r="69" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B69" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="44" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D69" s="44"/>
       <c r="E69" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F69" s="44"/>
       <c r="G69" s="44"/>
@@ -4160,17 +4252,17 @@
     </row>
     <row r="70" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B70" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="44" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D70" s="44"/>
       <c r="E70" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F70" s="44"/>
       <c r="G70" s="44"/>
@@ -4182,17 +4274,17 @@
     </row>
     <row r="71" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B71" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C71" s="44" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D71" s="44"/>
       <c r="E71" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F71" s="44"/>
       <c r="G71" s="44"/>
@@ -4204,17 +4296,17 @@
     </row>
     <row r="72" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B72" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C72" s="44" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D72" s="44"/>
       <c r="E72" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F72" s="44"/>
       <c r="G72" s="44"/>
@@ -4226,17 +4318,17 @@
     </row>
     <row r="73" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B73" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C73" s="44" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D73" s="44"/>
       <c r="E73" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F73" s="44"/>
       <c r="G73" s="44"/>
@@ -4246,41 +4338,48 @@
       <c r="M73" s="38"/>
       <c r="N73" s="38"/>
     </row>
-    <row r="74" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="74" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A74" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B74" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C74" s="44" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D74" s="44"/>
       <c r="E74" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F74" s="44"/>
       <c r="G74" s="44"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="44"/>
+      <c r="H74" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I74" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="J74" s="45" t="s">
+        <v>231</v>
+      </c>
       <c r="L74" s="38"/>
       <c r="M74" s="38"/>
       <c r="N74" s="38"/>
     </row>
     <row r="75" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B75" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="44" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D75" s="44"/>
       <c r="E75" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F75" s="44"/>
       <c r="G75" s="44"/>
@@ -4292,17 +4391,17 @@
     </row>
     <row r="76" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B76" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C76" s="44" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D76" s="44"/>
       <c r="E76" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F76" s="44"/>
       <c r="G76" s="44"/>
@@ -4314,17 +4413,17 @@
     </row>
     <row r="77" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C77" s="44" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D77" s="44"/>
       <c r="E77" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F77" s="44"/>
       <c r="G77" s="44"/>
@@ -4336,17 +4435,17 @@
     </row>
     <row r="78" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B78" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C78" s="44" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D78" s="44"/>
       <c r="E78" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F78" s="44"/>
       <c r="G78" s="44"/>
@@ -4358,17 +4457,17 @@
     </row>
     <row r="79" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C79" s="44" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D79" s="44"/>
       <c r="E79" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F79" s="44"/>
       <c r="G79" s="44"/>
@@ -4380,17 +4479,17 @@
     </row>
     <row r="80" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B80" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C80" s="44" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D80" s="44"/>
       <c r="E80" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F80" s="44"/>
       <c r="G80" s="44"/>
@@ -4402,17 +4501,17 @@
     </row>
     <row r="81" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B81" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C81" s="44" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D81" s="44"/>
       <c r="E81" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F81" s="44"/>
       <c r="G81" s="44"/>
@@ -4424,17 +4523,17 @@
     </row>
     <row r="82" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B82" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C82" s="44" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D82" s="44"/>
       <c r="E82" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F82" s="44"/>
       <c r="G82" s="44"/>
@@ -4446,17 +4545,17 @@
     </row>
     <row r="83" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B83" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D83" s="44"/>
       <c r="E83" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F83" s="44"/>
       <c r="G83" s="44"/>
@@ -4468,17 +4567,17 @@
     </row>
     <row r="84" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B84" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C84" s="44" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D84" s="44"/>
       <c r="E84" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F84" s="44"/>
       <c r="G84" s="44"/>
@@ -4490,17 +4589,17 @@
     </row>
     <row r="85" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B85" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C85" s="44" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D85" s="44"/>
       <c r="E85" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F85" s="44"/>
       <c r="G85" s="44"/>
@@ -4512,17 +4611,17 @@
     </row>
     <row r="86" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B86" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D86" s="44"/>
       <c r="E86" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F86" s="44"/>
       <c r="G86" s="44"/>
@@ -4534,17 +4633,17 @@
     </row>
     <row r="87" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B87" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C87" s="44" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D87" s="44"/>
       <c r="E87" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F87" s="44"/>
       <c r="G87" s="44"/>
@@ -4554,19 +4653,19 @@
       <c r="M87" s="38"/>
       <c r="N87" s="38"/>
     </row>
-    <row r="88" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="88" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A88" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B88" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C88" s="44" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D88" s="44"/>
       <c r="E88" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F88" s="44"/>
       <c r="G88" s="44"/>
@@ -4574,7 +4673,7 @@
         <v>33</v>
       </c>
       <c r="I88" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L88" s="38"/>
       <c r="M88" s="38"/>
@@ -4582,17 +4681,17 @@
     </row>
     <row r="89" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A89" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B89" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C89" s="44" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D89" s="44"/>
       <c r="E89" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F89" s="44"/>
       <c r="G89" s="44"/>
@@ -4604,17 +4703,17 @@
     </row>
     <row r="90" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A90" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B90" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="44" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D90" s="44"/>
       <c r="E90" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F90" s="44"/>
       <c r="G90" s="44"/>
@@ -4626,17 +4725,17 @@
     </row>
     <row r="91" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B91" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C91" s="44" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D91" s="44"/>
       <c r="E91" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F91" s="44"/>
       <c r="G91" s="44"/>
@@ -4648,17 +4747,17 @@
     </row>
     <row r="92" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A92" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B92" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C92" s="44" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D92" s="44"/>
       <c r="E92" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F92" s="44"/>
       <c r="G92" s="44"/>
@@ -4670,17 +4769,17 @@
     </row>
     <row r="93" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A93" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B93" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C93" s="44" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D93" s="44"/>
       <c r="E93" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F93" s="44"/>
       <c r="G93" s="44"/>
@@ -4692,17 +4791,17 @@
     </row>
     <row r="94" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A94" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B94" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C94" s="44" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D94" s="44"/>
       <c r="E94" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F94" s="44"/>
       <c r="G94" s="44"/>
@@ -4714,17 +4813,17 @@
     </row>
     <row r="95" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B95" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C95" s="44" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D95" s="44"/>
       <c r="E95" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F95" s="44"/>
       <c r="G95" s="44"/>
@@ -4736,17 +4835,17 @@
     </row>
     <row r="96" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A96" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B96" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C96" s="44" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D96" s="44"/>
       <c r="E96" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F96" s="44"/>
       <c r="G96" s="44"/>
@@ -4758,17 +4857,17 @@
     </row>
     <row r="97" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A97" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B97" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C97" s="44" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D97" s="44"/>
       <c r="E97" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F97" s="44"/>
       <c r="G97" s="44"/>
@@ -4780,17 +4879,17 @@
     </row>
     <row r="98" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A98" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B98" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C98" s="44" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D98" s="44"/>
       <c r="E98" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F98" s="44"/>
       <c r="G98" s="44"/>
@@ -4802,17 +4901,17 @@
     </row>
     <row r="99" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A99" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B99" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C99" s="44" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D99" s="44"/>
       <c r="E99" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F99" s="44"/>
       <c r="G99" s="44"/>
@@ -4822,19 +4921,19 @@
       <c r="M99" s="38"/>
       <c r="N99" s="38"/>
     </row>
-    <row r="100" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="100" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A100" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B100" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="44" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D100" s="44"/>
       <c r="E100" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F100" s="44"/>
       <c r="G100" s="44"/>
@@ -4842,7 +4941,7 @@
         <v>33</v>
       </c>
       <c r="I100" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L100" s="38"/>
       <c r="M100" s="38"/>
@@ -4850,17 +4949,17 @@
     </row>
     <row r="101" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A101" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B101" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C101" s="44" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D101" s="44"/>
       <c r="E101" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F101" s="44"/>
       <c r="G101" s="44"/>
@@ -4872,17 +4971,17 @@
     </row>
     <row r="102" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A102" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B102" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C102" s="44" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D102" s="44"/>
       <c r="E102" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F102" s="44"/>
       <c r="G102" s="44"/>
@@ -4894,17 +4993,17 @@
     </row>
     <row r="103" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A103" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B103" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C103" s="44" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D103" s="44"/>
       <c r="E103" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F103" s="44"/>
       <c r="G103" s="44"/>
@@ -4916,17 +5015,17 @@
     </row>
     <row r="104" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A104" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B104" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C104" s="44" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D104" s="44"/>
       <c r="E104" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F104" s="44"/>
       <c r="G104" s="44"/>
@@ -4936,19 +5035,19 @@
       <c r="M104" s="38"/>
       <c r="N104" s="38"/>
     </row>
-    <row r="105" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="105" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A105" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B105" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C105" s="44" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D105" s="44"/>
       <c r="E105" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F105" s="44"/>
       <c r="G105" s="44"/>
@@ -4956,7 +5055,7 @@
         <v>33</v>
       </c>
       <c r="I105" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L105" s="38"/>
       <c r="M105" s="38"/>
@@ -4964,17 +5063,17 @@
     </row>
     <row r="106" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A106" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B106" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C106" s="44" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D106" s="44"/>
       <c r="E106" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F106" s="44"/>
       <c r="G106" s="44"/>
@@ -4986,17 +5085,17 @@
     </row>
     <row r="107" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A107" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B107" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C107" s="44" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D107" s="44"/>
       <c r="E107" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F107" s="44"/>
       <c r="G107" s="44"/>
@@ -5008,17 +5107,17 @@
     </row>
     <row r="108" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A108" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B108" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="44" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D108" s="44"/>
       <c r="E108" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F108" s="44"/>
       <c r="G108" s="44"/>
@@ -5030,17 +5129,17 @@
     </row>
     <row r="109" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A109" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B109" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C109" s="44" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D109" s="44"/>
       <c r="E109" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F109" s="44"/>
       <c r="G109" s="44"/>
@@ -5052,17 +5151,17 @@
     </row>
     <row r="110" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A110" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B110" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C110" s="44" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D110" s="44"/>
       <c r="E110" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F110" s="44"/>
       <c r="G110" s="44"/>
@@ -5074,17 +5173,17 @@
     </row>
     <row r="111" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A111" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B111" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C111" s="44" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D111" s="44"/>
       <c r="E111" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F111" s="44"/>
       <c r="G111" s="44"/>
@@ -5096,17 +5195,17 @@
     </row>
     <row r="112" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A112" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B112" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C112" s="44" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D112" s="44"/>
       <c r="E112" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F112" s="44"/>
       <c r="G112" s="44"/>
@@ -5118,17 +5217,17 @@
     </row>
     <row r="113" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A113" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B113" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="44" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D113" s="44"/>
       <c r="E113" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F113" s="44"/>
       <c r="G113" s="44"/>
@@ -5138,19 +5237,19 @@
       <c r="M113" s="38"/>
       <c r="N113" s="38"/>
     </row>
-    <row r="114" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="114" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A114" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B114" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C114" s="44" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D114" s="44"/>
       <c r="E114" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F114" s="44"/>
       <c r="G114" s="44"/>
@@ -5158,25 +5257,25 @@
         <v>33</v>
       </c>
       <c r="I114" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L114" s="38"/>
       <c r="M114" s="38"/>
       <c r="N114" s="38"/>
     </row>
-    <row r="115" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="115" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A115" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B115" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C115" s="44" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D115" s="44"/>
       <c r="E115" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F115" s="44"/>
       <c r="G115" s="44"/>
@@ -5184,13 +5283,13 @@
         <v>33</v>
       </c>
       <c r="I115" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L115" s="38"/>
       <c r="M115" s="38"/>
       <c r="N115" s="38"/>
     </row>
-    <row r="116" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="116" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A116" s="38"/>
       <c r="B116" s="38"/>
       <c r="C116" s="44"/>
@@ -5204,19 +5303,19 @@
       <c r="M116" s="38"/>
       <c r="N116" s="38"/>
     </row>
-    <row r="117" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="117" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A117" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B117" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="44" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D117" s="44"/>
       <c r="E117" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F117" s="44"/>
       <c r="G117" s="44"/>
@@ -5224,7 +5323,7 @@
         <v>33</v>
       </c>
       <c r="I117" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L117" s="38"/>
       <c r="M117" s="38"/>
@@ -5232,17 +5331,17 @@
     </row>
     <row r="118" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A118" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B118" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C118" s="44" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D118" s="44"/>
       <c r="E118" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F118" s="44"/>
       <c r="G118" s="44"/>
@@ -5254,17 +5353,17 @@
     </row>
     <row r="119" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A119" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B119" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C119" s="44" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D119" s="44"/>
       <c r="E119" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F119" s="44"/>
       <c r="G119" s="44"/>
@@ -5276,17 +5375,17 @@
     </row>
     <row r="120" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A120" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B120" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C120" s="44" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D120" s="44"/>
       <c r="E120" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F120" s="44"/>
       <c r="G120" s="44"/>
@@ -5296,19 +5395,19 @@
       <c r="M120" s="38"/>
       <c r="N120" s="38"/>
     </row>
-    <row r="121" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="121" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A121" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B121" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C121" s="44" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D121" s="44"/>
       <c r="E121" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F121" s="44"/>
       <c r="G121" s="44"/>
@@ -5316,7 +5415,7 @@
         <v>33</v>
       </c>
       <c r="I121" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L121" s="38"/>
       <c r="M121" s="38"/>
@@ -5324,17 +5423,17 @@
     </row>
     <row r="122" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A122" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B122" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C122" s="44" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D122" s="44"/>
       <c r="E122" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F122" s="44"/>
       <c r="G122" s="44"/>
@@ -5344,19 +5443,19 @@
       <c r="M122" s="38"/>
       <c r="N122" s="38"/>
     </row>
-    <row r="123" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="123" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A123" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B123" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C123" s="44" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D123" s="44"/>
       <c r="E123" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F123" s="44"/>
       <c r="G123" s="44"/>
@@ -5364,25 +5463,25 @@
         <v>33</v>
       </c>
       <c r="I123" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L123" s="38"/>
       <c r="M123" s="38"/>
       <c r="N123" s="38"/>
     </row>
-    <row r="124" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="124" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A124" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B124" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C124" s="44" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D124" s="44"/>
       <c r="E124" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F124" s="44"/>
       <c r="G124" s="44"/>
@@ -5390,7 +5489,7 @@
         <v>33</v>
       </c>
       <c r="I124" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L124" s="38"/>
       <c r="M124" s="38"/>
@@ -5398,17 +5497,17 @@
     </row>
     <row r="125" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A125" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B125" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C125" s="44" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D125" s="44"/>
       <c r="E125" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F125" s="44"/>
       <c r="G125" s="44"/>
@@ -5420,17 +5519,17 @@
     </row>
     <row r="126" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A126" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B126" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="44" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D126" s="44"/>
       <c r="E126" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F126" s="44"/>
       <c r="G126" s="44"/>
@@ -5442,17 +5541,17 @@
     </row>
     <row r="127" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A127" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B127" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="44" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D127" s="44"/>
       <c r="E127" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F127" s="44"/>
       <c r="G127" s="44"/>
@@ -5462,19 +5561,19 @@
       <c r="M127" s="38"/>
       <c r="N127" s="38"/>
     </row>
-    <row r="128" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="128" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A128" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B128" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="44" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D128" s="44"/>
       <c r="E128" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F128" s="44"/>
       <c r="G128" s="44"/>
@@ -5482,25 +5581,25 @@
         <v>33</v>
       </c>
       <c r="I128" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L128" s="38"/>
       <c r="M128" s="38"/>
       <c r="N128" s="38"/>
     </row>
-    <row r="129" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="129" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A129" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B129" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="44" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D129" s="44"/>
       <c r="E129" s="44" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F129" s="44"/>
       <c r="G129" s="44"/>
@@ -5511,26 +5610,26 @@
         <v>20</v>
       </c>
       <c r="J129" s="49" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K129" s="49"/>
       <c r="L129" s="38"/>
       <c r="M129" s="38"/>
       <c r="N129" s="38"/>
     </row>
-    <row r="130" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="130" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A130" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B130" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="44" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D130" s="44"/>
       <c r="E130" s="44" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F130" s="44"/>
       <c r="G130" s="44"/>
@@ -5541,26 +5640,26 @@
         <v>20</v>
       </c>
       <c r="J130" s="49" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K130" s="49"/>
       <c r="L130" s="38"/>
       <c r="M130" s="38"/>
       <c r="N130" s="38"/>
     </row>
-    <row r="131" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="131" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A131" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B131" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="44" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D131" s="44"/>
       <c r="E131" s="44" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F131" s="44"/>
       <c r="G131" s="44"/>
@@ -5571,25 +5670,25 @@
         <v>20</v>
       </c>
       <c r="J131" s="45" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L131" s="38"/>
       <c r="M131" s="38"/>
       <c r="N131" s="38"/>
     </row>
-    <row r="132" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="132" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A132" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B132" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="44" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D132" s="44"/>
       <c r="E132" s="44" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
@@ -5600,26 +5699,26 @@
         <v>20</v>
       </c>
       <c r="J132" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K132"/>
       <c r="L132" s="38"/>
       <c r="M132" s="38"/>
       <c r="N132" s="38"/>
     </row>
-    <row r="133" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="133" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A133" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B133" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="44" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D133" s="44"/>
       <c r="E133" s="44" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F133" s="44"/>
       <c r="G133" s="44"/>
@@ -5630,26 +5729,26 @@
         <v>20</v>
       </c>
       <c r="J133" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="K133"/>
       <c r="L133" s="38"/>
       <c r="M133" s="38"/>
       <c r="N133" s="38"/>
     </row>
-    <row r="134" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="134" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A134" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B134" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="44" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D134" s="44"/>
       <c r="E134" s="44" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F134" s="44"/>
       <c r="G134" s="44"/>
@@ -5660,48 +5759,55 @@
         <v>20</v>
       </c>
       <c r="J134" s="49" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="K134" s="49"/>
       <c r="L134" s="38"/>
       <c r="M134" s="38"/>
       <c r="N134" s="38"/>
     </row>
-    <row r="135" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="135" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A135" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B135" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="44" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D135" s="44"/>
       <c r="E135" s="44" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F135" s="44"/>
       <c r="G135" s="44"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="44"/>
+      <c r="H135" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I135" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J135" s="45" t="s">
+        <v>307</v>
+      </c>
       <c r="L135" s="38"/>
       <c r="M135" s="38"/>
       <c r="N135" s="38"/>
     </row>
-    <row r="136" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="136" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A136" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B136" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="44" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D136" s="44"/>
       <c r="E136" s="44" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F136" s="44"/>
       <c r="G136" s="44"/>
@@ -5712,7 +5818,7 @@
         <v>20</v>
       </c>
       <c r="J136" s="45" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="L136" s="38"/>
       <c r="M136" s="38"/>
@@ -5720,17 +5826,17 @@
     </row>
     <row r="137" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A137" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B137" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C137" s="44" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D137" s="44"/>
       <c r="E137" s="44" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="F137" s="44"/>
       <c r="G137" s="44"/>
@@ -5740,19 +5846,19 @@
       <c r="M137" s="38"/>
       <c r="N137" s="38"/>
     </row>
-    <row r="138" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="138" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A138" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B138" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C138" s="44" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D138" s="44"/>
       <c r="E138" s="44" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F138" s="44"/>
       <c r="G138" s="44"/>
@@ -5760,25 +5866,25 @@
         <v>33</v>
       </c>
       <c r="I138" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L138" s="38"/>
       <c r="M138" s="38"/>
       <c r="N138" s="38"/>
     </row>
-    <row r="139" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="139" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A139" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B139" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C139" s="44" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D139" s="44"/>
       <c r="E139" s="44" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F139" s="44"/>
       <c r="G139" s="44"/>
@@ -5786,25 +5892,25 @@
         <v>33</v>
       </c>
       <c r="I139" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L139" s="44"/>
       <c r="M139" s="38"/>
       <c r="N139" s="38"/>
     </row>
-    <row r="140" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="140" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A140" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B140" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C140" s="44" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D140" s="44"/>
       <c r="E140" s="44" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F140" s="44"/>
       <c r="G140" s="44"/>
@@ -5812,7 +5918,7 @@
         <v>33</v>
       </c>
       <c r="I140" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L140" s="38"/>
       <c r="M140" s="38"/>
@@ -5820,17 +5926,17 @@
     </row>
     <row r="141" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A141" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B141" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C141" s="44" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D141" s="44"/>
       <c r="E141" s="44" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F141" s="44"/>
       <c r="G141" s="44"/>
@@ -5842,17 +5948,17 @@
     </row>
     <row r="142" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A142" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B142" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C142" s="44" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D142" s="44"/>
       <c r="E142" s="44" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F142" s="44"/>
       <c r="G142" s="44"/>
@@ -5862,19 +5968,19 @@
       <c r="M142" s="38"/>
       <c r="N142" s="38"/>
     </row>
-    <row r="143" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="143" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A143" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B143" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C143" s="44" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D143" s="44"/>
       <c r="E143" s="44" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F143" s="44"/>
       <c r="G143" s="44"/>
@@ -5882,28 +5988,28 @@
         <v>33</v>
       </c>
       <c r="I143" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J143" s="45" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="L143" s="38"/>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
     </row>
-    <row r="144" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="144" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A144" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B144" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C144" s="44" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D144" s="44"/>
       <c r="E144" s="44" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F144" s="44"/>
       <c r="G144" s="44"/>
@@ -5911,28 +6017,28 @@
         <v>33</v>
       </c>
       <c r="I144" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J144" s="45" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="L144" s="38"/>
       <c r="M144" s="38"/>
       <c r="N144" s="38"/>
     </row>
-    <row r="145" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="145" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A145" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B145" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C145" s="44" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D145" s="44"/>
       <c r="E145" s="44" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F145" s="44"/>
       <c r="G145" s="44"/>
@@ -5940,28 +6046,28 @@
         <v>33</v>
       </c>
       <c r="I145" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J145" s="45" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="L145" s="38"/>
       <c r="M145" s="38"/>
       <c r="N145" s="38"/>
     </row>
-    <row r="146" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="146" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A146" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B146" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C146" s="44" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D146" s="44"/>
       <c r="E146" s="44" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F146" s="44"/>
       <c r="G146" s="44"/>
@@ -5969,50 +6075,57 @@
         <v>33</v>
       </c>
       <c r="I146" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J146" s="45" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="L146" s="38"/>
       <c r="M146" s="38"/>
       <c r="N146" s="38"/>
     </row>
-    <row r="147" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="147" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A147" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B147" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C147" s="44" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D147" s="44"/>
       <c r="E147" s="44" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F147" s="44"/>
       <c r="G147" s="44"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="44"/>
+      <c r="H147" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I147" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J147" s="45" t="s">
+        <v>337</v>
+      </c>
       <c r="L147" s="38"/>
       <c r="M147" s="38"/>
       <c r="N147" s="38"/>
     </row>
-    <row r="148" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="148" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A148" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B148" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C148" s="44" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D148" s="44"/>
       <c r="E148" s="44" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F148" s="44"/>
       <c r="G148" s="44"/>
@@ -6023,25 +6136,25 @@
         <v>20</v>
       </c>
       <c r="J148" s="49" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="L148" s="38"/>
       <c r="M148" s="38"/>
       <c r="N148" s="38"/>
     </row>
-    <row r="149" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="149" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A149" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B149" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C149" s="44" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D149" s="44"/>
       <c r="E149" s="44" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F149" s="44"/>
       <c r="G149" s="44"/>
@@ -6052,25 +6165,25 @@
         <v>20</v>
       </c>
       <c r="J149" s="45" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="L149" s="38"/>
       <c r="M149" s="38"/>
       <c r="N149" s="38"/>
     </row>
-    <row r="150" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="150" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A150" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B150" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C150" s="44" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D150" s="44"/>
       <c r="E150" s="44" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F150" s="44"/>
       <c r="G150" s="44"/>
@@ -6078,10 +6191,10 @@
         <v>33</v>
       </c>
       <c r="I150" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J150" s="45" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="L150" s="38"/>
       <c r="M150" s="38"/>
@@ -6089,19 +6202,19 @@
     </row>
     <row r="151" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A151" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B151" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C151" s="44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D151" s="44" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E151" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F151" s="44"/>
       <c r="G151" s="44"/>
@@ -6113,19 +6226,19 @@
     </row>
     <row r="152" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A152" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B152" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C152" s="44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D152" s="44" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E152" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F152" s="44"/>
       <c r="G152" s="44"/>
@@ -6137,19 +6250,19 @@
     </row>
     <row r="153" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A153" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B153" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C153" s="44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D153" s="44" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E153" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F153" s="44"/>
       <c r="G153" s="44"/>
@@ -6161,19 +6274,19 @@
     </row>
     <row r="154" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A154" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B154" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C154" s="44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D154" s="44" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E154" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F154" s="44"/>
       <c r="G154" s="44"/>
@@ -6185,19 +6298,19 @@
     </row>
     <row r="155" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A155" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B155" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C155" s="44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D155" s="44" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E155" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F155" s="44"/>
       <c r="G155" s="44"/>
@@ -6209,19 +6322,19 @@
     </row>
     <row r="156" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A156" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B156" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C156" s="44" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D156" s="44" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E156" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F156" s="44"/>
       <c r="G156" s="44"/>
@@ -6233,19 +6346,19 @@
     </row>
     <row r="157" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A157" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B157" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C157" s="44" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D157" s="44" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E157" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F157" s="44"/>
       <c r="G157" s="44"/>
@@ -6257,19 +6370,19 @@
     </row>
     <row r="158" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A158" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B158" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C158" s="44" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D158" s="44" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E158" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F158" s="44"/>
       <c r="G158" s="44"/>
@@ -6281,19 +6394,19 @@
     </row>
     <row r="159" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A159" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B159" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C159" s="44" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D159" s="44" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E159" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F159" s="44"/>
       <c r="G159" s="44"/>
@@ -6305,19 +6418,19 @@
     </row>
     <row r="160" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A160" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B160" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C160" s="44" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D160" s="44" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E160" s="44" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F160" s="44"/>
       <c r="G160" s="44"/>
@@ -6329,19 +6442,19 @@
     </row>
     <row r="161" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A161" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B161" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C161" s="44" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D161" s="44" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E161" s="44" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F161" s="44"/>
       <c r="G161" s="44"/>
@@ -6351,133 +6464,140 @@
       <c r="M161" s="38"/>
       <c r="N161" s="38"/>
     </row>
-    <row r="162" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="162" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A162" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B162" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C162" s="44" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D162" s="44"/>
       <c r="E162" s="44" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F162" s="44"/>
       <c r="G162" s="44"/>
       <c r="H162" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I162" s="44" t="s">
         <v>20</v>
       </c>
       <c r="J162" s="52" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="L162" s="38"/>
       <c r="M162" s="38"/>
       <c r="N162" s="38"/>
     </row>
-    <row r="163" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="163" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A163" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B163" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C163" s="44" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D163" s="44"/>
       <c r="E163" s="44" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="F163" s="44"/>
       <c r="G163" s="44"/>
-      <c r="H163" s="13"/>
-      <c r="I163" s="44"/>
+      <c r="H163" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="I163" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J163" s="45" t="s">
+        <v>359</v>
+      </c>
       <c r="L163" s="38"/>
       <c r="M163" s="38"/>
       <c r="N163" s="38"/>
     </row>
-    <row r="164" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="164" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A164" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B164" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C164" s="44" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="D164" s="44"/>
       <c r="E164" s="44" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F164" s="44"/>
       <c r="G164" s="44"/>
       <c r="H164" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I164" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L164" s="38"/>
       <c r="M164" s="38"/>
       <c r="N164" s="38"/>
     </row>
-    <row r="165" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="165" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A165" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B165" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C165" s="44" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D165" s="44"/>
       <c r="E165" s="44" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F165" s="44"/>
       <c r="G165" s="44"/>
       <c r="H165" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I165" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L165" s="38"/>
       <c r="M165" s="38"/>
       <c r="N165" s="38"/>
     </row>
-    <row r="166" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="166" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A166" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B166" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C166" s="44" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="D166" s="44"/>
       <c r="E166" s="44" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F166" s="44"/>
       <c r="G166" s="44"/>
       <c r="H166" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I166" s="44" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J166" s="45" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L166" s="38"/>
       <c r="M166" s="38"/>
@@ -6485,17 +6605,17 @@
     </row>
     <row r="167" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A167" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B167" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C167" s="44" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D167" s="44"/>
       <c r="E167" s="44" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F167" s="44"/>
       <c r="G167" s="44"/>
@@ -6507,17 +6627,17 @@
     </row>
     <row r="168" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A168" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B168" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C168" s="44" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D168" s="44"/>
       <c r="E168" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F168" s="44"/>
       <c r="G168" s="44"/>
@@ -6529,17 +6649,17 @@
     </row>
     <row r="169" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A169" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B169" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C169" s="44" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D169" s="44"/>
       <c r="E169" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F169" s="44"/>
       <c r="G169" s="44"/>
@@ -6551,17 +6671,17 @@
     </row>
     <row r="170" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A170" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B170" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C170" s="44" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D170" s="44"/>
       <c r="E170" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F170" s="44"/>
       <c r="G170" s="44"/>
@@ -6573,17 +6693,17 @@
     </row>
     <row r="171" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A171" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B171" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C171" s="44" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D171" s="44"/>
       <c r="E171" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F171" s="44"/>
       <c r="G171" s="44"/>
@@ -6595,17 +6715,17 @@
     </row>
     <row r="172" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A172" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B172" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C172" s="44" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D172" s="44"/>
       <c r="E172" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F172" s="44"/>
       <c r="G172" s="44"/>
@@ -6617,17 +6737,17 @@
     </row>
     <row r="173" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A173" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B173" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C173" s="44" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D173" s="44"/>
       <c r="E173" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F173" s="44"/>
       <c r="G173" s="44"/>
@@ -6639,17 +6759,17 @@
     </row>
     <row r="174" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A174" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B174" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C174" s="44" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D174" s="44"/>
       <c r="E174" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F174" s="44"/>
       <c r="G174" s="44"/>
@@ -6661,17 +6781,17 @@
     </row>
     <row r="175" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A175" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B175" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C175" s="44" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D175" s="44"/>
       <c r="E175" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F175" s="44"/>
       <c r="G175" s="44"/>
@@ -6683,17 +6803,17 @@
     </row>
     <row r="176" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A176" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B176" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C176" s="44" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D176" s="44"/>
       <c r="E176" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F176" s="44"/>
       <c r="G176" s="44"/>
@@ -6705,17 +6825,17 @@
     </row>
     <row r="177" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A177" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B177" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C177" s="44" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D177" s="44"/>
       <c r="E177" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F177" s="44"/>
       <c r="G177" s="44"/>
@@ -6727,17 +6847,17 @@
     </row>
     <row r="178" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A178" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B178" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C178" s="44" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D178" s="44"/>
       <c r="E178" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F178" s="44"/>
       <c r="G178" s="44"/>
@@ -6749,17 +6869,17 @@
     </row>
     <row r="179" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A179" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B179" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C179" s="44" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D179" s="44"/>
       <c r="E179" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F179" s="44"/>
       <c r="G179" s="44"/>
@@ -6771,17 +6891,17 @@
     </row>
     <row r="180" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A180" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B180" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C180" s="44" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D180" s="44"/>
       <c r="E180" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F180" s="44"/>
       <c r="G180" s="44"/>
@@ -6793,17 +6913,17 @@
     </row>
     <row r="181" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A181" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B181" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C181" s="44" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D181" s="44"/>
       <c r="E181" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F181" s="44"/>
       <c r="G181" s="44"/>
@@ -6815,17 +6935,17 @@
     </row>
     <row r="182" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A182" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B182" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C182" s="44" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D182" s="44"/>
       <c r="E182" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F182" s="44"/>
       <c r="G182" s="44"/>
@@ -6837,17 +6957,17 @@
     </row>
     <row r="183" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A183" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B183" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="44" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D183" s="44"/>
       <c r="E183" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F183" s="44"/>
       <c r="G183" s="44"/>
@@ -6859,17 +6979,17 @@
     </row>
     <row r="184" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A184" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B184" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C184" s="44" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D184" s="44"/>
       <c r="E184" s="44" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F184" s="44"/>
       <c r="G184" s="44"/>
@@ -6881,17 +7001,17 @@
     </row>
     <row r="185" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A185" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B185" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C185" s="44" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="D185" s="44"/>
       <c r="E185" s="44" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F185" s="44"/>
       <c r="G185" s="44"/>
@@ -6903,17 +7023,17 @@
     </row>
     <row r="186" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A186" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B186" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C186" s="44" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D186" s="44"/>
       <c r="E186" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F186" s="44"/>
       <c r="G186" s="44"/>
@@ -6925,17 +7045,17 @@
     </row>
     <row r="187" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A187" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B187" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C187" s="44" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D187" s="44"/>
       <c r="E187" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F187" s="44"/>
       <c r="G187" s="44"/>
@@ -6947,17 +7067,17 @@
     </row>
     <row r="188" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A188" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B188" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C188" s="44" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="D188" s="44"/>
       <c r="E188" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F188" s="44"/>
       <c r="G188" s="44"/>
@@ -6969,17 +7089,17 @@
     </row>
     <row r="189" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A189" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B189" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C189" s="44" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="D189" s="44"/>
       <c r="E189" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F189" s="44"/>
       <c r="G189" s="44"/>
@@ -6991,17 +7111,17 @@
     </row>
     <row r="190" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
       <c r="A190" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B190" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C190" s="44" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D190" s="44"/>
       <c r="E190" s="44" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F190" s="44"/>
       <c r="G190" s="44"/>
@@ -7011,81 +7131,85 @@
       <c r="M190" s="38"/>
       <c r="N190" s="38"/>
     </row>
-    <row r="191" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="191" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A191" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B191" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C191" s="44" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D191" s="44"/>
       <c r="E191" s="44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F191" s="44"/>
       <c r="G191" s="44"/>
       <c r="H191" s="44" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="I191" s="44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L191" s="38"/>
       <c r="M191" s="38"/>
       <c r="N191" s="38"/>
     </row>
-    <row r="192" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="192" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A192" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B192" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C192" s="44" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D192" s="44"/>
       <c r="E192" s="44" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F192" s="44"/>
       <c r="G192" s="44"/>
-      <c r="H192" s="13"/>
-      <c r="I192" s="44"/>
+      <c r="H192" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="I192" s="44" t="s">
+        <v>20</v>
+      </c>
       <c r="J192" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L192" s="38"/>
       <c r="M192" s="38"/>
       <c r="N192" s="38"/>
     </row>
-    <row r="193" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1">
+    <row r="193" spans="1:14" s="45" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A193" s="38" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B193" s="38" t="s">
         <v>13</v>
       </c>
       <c r="C193" s="44" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D193" s="44"/>
       <c r="E193" s="44" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="F193" s="44"/>
       <c r="G193" s="44"/>
       <c r="H193" s="13" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="I193" s="44" t="s">
         <v>20</v>
       </c>
       <c r="J193" s="45" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L193" s="38"/>
       <c r="M193" s="38"/>
@@ -7095,7 +7219,16 @@
     <row r="195" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1"/>
     <row r="196" spans="1:14" s="45" customFormat="1" ht="15" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:N193" xr:uid="{BFC7790F-BFFF-4C75-BDC2-60CFF6F25A9C}"/>
+  <autoFilter ref="A1:N193" xr:uid="{BFC7790F-BFFF-4C75-BDC2-60CFF6F25A9C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Yes"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="G25" r:id="rId1" xr:uid="{30DDA83A-16FC-4539-80C2-63721D631168}"/>
     <hyperlink ref="G26" r:id="rId2" xr:uid="{650F426C-DC0B-4659-8728-6C04809BB9F2}"/>
@@ -7120,167 +7253,167 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="E1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="E2" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B5" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="48" customFormat="1" hidden="1">
       <c r="A7" s="48" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="54" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C11" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="54"/>
       <c r="B12" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C12" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C14" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -7306,7 +7439,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>4</v>
@@ -7314,159 +7447,159 @@
     </row>
     <row r="2" spans="1:4" ht="28.9">
       <c r="A2" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.9">
       <c r="A5" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="57.6">
       <c r="A6" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.9">
       <c r="A7" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="43.15">
       <c r="A8" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="28.9">
       <c r="A9" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -7476,7 +7609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A992C999-E41E-4FE1-A6DD-B51EC6A13236}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
@@ -7486,13 +7619,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D1" t="s">
         <v>20</v>
@@ -7500,13 +7633,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -7514,13 +7647,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
@@ -7528,13 +7661,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -7542,13 +7675,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -7556,13 +7689,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C6" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -7570,13 +7703,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C7" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -7584,13 +7717,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C8" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -7598,13 +7731,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -7612,13 +7745,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
@@ -7626,13 +7759,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C11" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
@@ -7643,10 +7776,10 @@
         <v>21</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C12" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -7654,13 +7787,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C13" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -7668,13 +7801,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C14" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -7682,13 +7815,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="49" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C15" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -7696,13 +7829,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="49" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -7710,13 +7843,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="45" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -7724,13 +7857,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="49" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
@@ -7738,13 +7871,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="45" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C19" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
@@ -7752,13 +7885,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
@@ -7766,13 +7899,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C21" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
@@ -7780,13 +7913,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C22" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
@@ -7794,13 +7927,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B23" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C23" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
@@ -7808,13 +7941,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C24" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
@@ -7822,13 +7955,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="52" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -7836,13 +7969,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C26" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -7850,13 +7983,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C27" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -7864,237 +7997,373 @@
     </row>
     <row r="28" spans="1:4">
       <c r="B28" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C28" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="D28" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D29" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="B30" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C30" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D30" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="B31" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C31" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D31" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="B32" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C32" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D32" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="B33" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C33" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D33" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="B34" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C34" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D34" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C35" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D35" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C36" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D36" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C37" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D37" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C38" t="s">
-        <v>441</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C39" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D39" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="B40" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C40" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D40" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="B41" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C41" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="D41" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="B42" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C42" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D42" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="B43" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C43" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D43" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="B44" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C44" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D45" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="B46" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C46" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C47" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D47" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+        <v>334</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C48" t="s">
+        <v>461</v>
+      </c>
+      <c r="D48" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>343</v>
+      </c>
+      <c r="B49" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C49" t="s">
+        <v>462</v>
+      </c>
+      <c r="D49" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>318</v>
+        <v>325</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C50" t="s">
+        <v>463</v>
+      </c>
+      <c r="D50" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>328</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C51" t="s">
+        <v>464</v>
+      </c>
+      <c r="D51" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>365</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C52" t="s">
+        <v>465</v>
+      </c>
+      <c r="D52" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>331</v>
+      </c>
+      <c r="B53" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C53" t="s">
+        <v>466</v>
+      </c>
+      <c r="D53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>467</v>
+      </c>
+      <c r="B54" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="C54" t="s">
+        <v>468</v>
+      </c>
+      <c r="D54" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>359</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="48" t="s">
+        <v>307</v>
+      </c>
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="48" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -8104,17 +8373,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100242DFFCF6AE4E640AF3FB52BFDDBD969" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="41a7506b10de41b759a30512e3cc06b7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5dcb083e-b3fa-493a-b8b9-b159a5a2f1a5" xmlns:ns3="dcfdd7bb-dcfb-4a5a-b3e2-bf8ae539425f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6928cf4eeac1c874d897ac6bc1348b62" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100242DFFCF6AE4E640AF3FB52BFDDBD969" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2de0cd45cfbbf6b724b7465c4301eef">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5dcb083e-b3fa-493a-b8b9-b159a5a2f1a5" xmlns:ns3="dcfdd7bb-dcfb-4a5a-b3e2-bf8ae539425f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="14b4b6b66d66a6690ae4f3f8ea86bf73" ns2:_="" ns3:_="">
     <xsd:import namespace="5dcb083e-b3fa-493a-b8b9-b159a5a2f1a5"/>
     <xsd:import namespace="dcfdd7bb-dcfb-4a5a-b3e2-bf8ae539425f"/>
     <xsd:element name="properties">
@@ -8133,6 +8393,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -8190,6 +8451,11 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -8307,6 +8573,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8319,11 +8594,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171E9F81-3D6D-4D04-99D6-49032BF73AF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10DD8E0A-B40A-4A0F-AA6D-3C8445EC44F8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3591E490-83C0-48D1-BA9D-309679F37403}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171E9F81-3D6D-4D04-99D6-49032BF73AF2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
